--- a/tools/importer/reports/import-parents-learners-page.report.xlsx
+++ b/tools/importer/reports/import-parents-learners-page.report.xlsx
@@ -40,7 +40,7 @@
     <t>en-gb/schools/secondary/parents-learners.report.json</t>
   </si>
   <si>
-    <t>["cards-linked","cards-linked","cards-linked","columns-promo","cards-topic","cards-topic","cards-topic","cards-topic","columns-info","columns-social","columns-social"]</t>
+    <t>["hero-landing","cards-linked","columns-promo","cards-topic","columns-info","columns-social"]</t>
   </si>
   <si>
     <t>en-gb/schools/secondary/parents-learners</t>
@@ -52,7 +52,7 @@
     <t>parents-learners-page</t>
   </si>
   <si>
-    <t>2026-03-09T13:42:40.705Z</t>
+    <t>2026-03-10T22:05:07.078Z</t>
   </si>
   <si>
     <t>Secondary students and parents | Pearson UK</t>
